--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F182683F-B93E-46B4-9336-EDE1619B6949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19245C7-9EC5-4AFF-AD12-51CE3FCFE157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -287,9 +287,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -336,6 +333,9 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -723,13 +723,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -737,7 +737,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -745,7 +745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -761,14 +761,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -779,7 +779,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -790,7 +790,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -801,7 +801,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -812,7 +812,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -832,17 +832,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -855,17 +855,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -879,13 +879,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -893,7 +893,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -901,10 +901,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -916,9 +916,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -1021,85 +1021,85 @@
         <v>35</v>
       </c>
       <c r="D2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>81</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" t="s">
         <v>82</v>
       </c>
-      <c r="G2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" t="s">
         <v>83</v>
       </c>
-      <c r="I2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>84</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>85</v>
-      </c>
-      <c r="M2" t="s">
-        <v>86</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="S2" t="s">
         <v>87</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="S2" t="s">
-        <v>88</v>
-      </c>
-      <c r="T2" s="8" t="s">
+      <c r="U2" t="s">
         <v>89</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>90</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>91</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>92</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>93</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>94</v>
       </c>
-      <c r="Z2" t="s">
-        <v>95</v>
-      </c>
       <c r="AA2" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1110,15 +1110,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1160,14 +1160,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1191,17 +1191,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1215,47 +1215,47 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>44</v>
       </c>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19245C7-9EC5-4AFF-AD12-51CE3FCFE157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403FB702-E371-4473-817F-CAEFDF6F3D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="99">
   <si>
     <t>James Craven</t>
   </si>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>View All Company List</t>
+  </si>
+  <si>
+    <t>122209-Buyers List-Tuck</t>
   </si>
 </sst>
 </file>
@@ -1109,12 +1115,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1149,6 +1155,14 @@
       </c>
       <c r="C3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403FB702-E371-4473-817F-CAEFDF6F3D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2E0272-5C92-4E71-A6DB-913B35E3DC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>A-Gas</t>
   </si>
   <si>
-    <t>Bayswater Partial Monetization</t>
-  </si>
-  <si>
     <t>View All</t>
   </si>
   <si>
@@ -342,6 +339,9 @@
   </si>
   <si>
     <t>122209-Buyers List-Tuck</t>
+  </si>
+  <si>
+    <t>Bayswater Dividend Recap</t>
   </si>
 </sst>
 </file>
@@ -729,13 +729,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -743,7 +743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -751,12 +751,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
         <v>47</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -767,14 +767,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -782,10 +782,10 @@
         <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -793,10 +793,10 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -804,21 +804,21 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -826,7 +826,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -838,17 +838,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -861,17 +861,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -885,13 +885,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -899,7 +899,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -907,10 +907,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -922,190 +922,190 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AD1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>79</v>
-      </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
         <v>80</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" t="s">
         <v>81</v>
       </c>
-      <c r="G2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" t="s">
         <v>82</v>
       </c>
-      <c r="I2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>83</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>84</v>
-      </c>
-      <c r="M2" t="s">
-        <v>85</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="s">
         <v>86</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="S2" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T2" s="8" t="s">
+      <c r="U2" t="s">
         <v>88</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>89</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>90</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>91</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>92</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>93</v>
       </c>
-      <c r="Z2" t="s">
-        <v>94</v>
-      </c>
       <c r="AA2" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1116,15 +1116,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.5546875" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1157,12 +1157,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s">
         <v>97</v>
-      </c>
-      <c r="C4" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1174,14 +1174,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1205,17 +1205,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1229,49 +1229,49 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E2E0272-5C92-4E71-A6DB-913B35E3DC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0899C9-D835-4358-A621-8F65F8B7FA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -200,9 +200,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -332,9 +329,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>View All Company List</t>
   </si>
   <si>
@@ -342,6 +336,12 @@
   </si>
   <si>
     <t>Bayswater Dividend Recap</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -809,7 +809,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
@@ -923,6 +923,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -935,177 +938,177 @@
         <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
         <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" t="s">
         <v>81</v>
       </c>
-      <c r="I2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>82</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>83</v>
-      </c>
-      <c r="M2" t="s">
-        <v>84</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" t="s">
         <v>85</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="S2" t="s">
         <v>85</v>
       </c>
-      <c r="Q2" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="S2" t="s">
-        <v>86</v>
-      </c>
-      <c r="T2" s="8" t="s">
+      <c r="U2" t="s">
         <v>87</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>88</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>89</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>90</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>91</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>92</v>
       </c>
-      <c r="Z2" t="s">
-        <v>93</v>
-      </c>
       <c r="AA2" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1159,10 +1162,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0899C9-D835-4358-A621-8F65F8B7FA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFE9EE9-2EB7-4CA0-ABA1-BCCE8CBA6394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -341,7 +341,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -729,13 +729,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -743,7 +743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -767,14 +767,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -785,7 +785,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -796,7 +796,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -807,7 +807,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -818,7 +818,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -838,17 +838,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -861,17 +861,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -885,13 +885,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -899,7 +899,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -907,10 +907,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -922,12 +922,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -1119,15 +1119,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.5546875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>94</v>
       </c>
@@ -1177,14 +1177,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1208,17 +1208,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1232,47 +1232,47 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFE9EE9-2EB7-4CA0-ABA1-BCCE8CBA6394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3567D10-BD24-47E2-B598-485012F43363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -1185,10 +1185,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F182683F-B93E-46B4-9336-EDE1619B6949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0D52D8-DF14-4592-92B1-516B2ED7A05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -19,10 +19,11 @@
     <sheet name="Opportunities" sheetId="5" r:id="rId4"/>
     <sheet name="AddOpportunity" sheetId="12" r:id="rId5"/>
     <sheet name="FilterSections" sheetId="6" r:id="rId6"/>
-    <sheet name="NewOpportunityCounterparty" sheetId="7" r:id="rId7"/>
-    <sheet name="CounterpartyContact" sheetId="8" r:id="rId8"/>
-    <sheet name="CounterpartiesPageButton" sheetId="9" r:id="rId9"/>
-    <sheet name="OpportunityWithJobType" sheetId="11" r:id="rId10"/>
+    <sheet name="CounterpartiesButton" sheetId="13" r:id="rId7"/>
+    <sheet name="NewOpportunityCounterparty" sheetId="7" r:id="rId8"/>
+    <sheet name="CounterpartyContact" sheetId="8" r:id="rId9"/>
+    <sheet name="CounterpartiesPageButton" sheetId="9" r:id="rId10"/>
+    <sheet name="OpportunityWithJobType" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="100">
   <si>
     <t>James Craven</t>
   </si>
@@ -140,9 +141,6 @@
     <t>Add Counterparties</t>
   </si>
   <si>
-    <t>Import with Dataloader</t>
-  </si>
-  <si>
     <t>Export Data</t>
   </si>
   <si>
@@ -173,12 +171,6 @@
     <t>Adeka Corporation</t>
   </si>
   <si>
-    <t>A-Gas</t>
-  </si>
-  <si>
-    <t>Bayswater Partial Monetization</t>
-  </si>
-  <si>
     <t>View All</t>
   </si>
   <si>
@@ -188,9 +180,6 @@
     <t>Not Close/Dead/Hold/Engaged</t>
   </si>
   <si>
-    <t>Gemma Hardy</t>
-  </si>
-  <si>
     <t>CAO</t>
   </si>
   <si>
@@ -203,9 +192,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -287,55 +273,79 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
+    <t>Dealership &amp; Rental Services</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>HL Capital, Inc.</t>
+  </si>
+  <si>
+    <t>Do Not Disclose</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Public Equity</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Chris Lord</t>
+  </si>
+  <si>
+    <t>Yes, separate signed agreement</t>
+  </si>
+  <si>
+    <t>Cleared</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>Consulting</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>View All Company List</t>
+  </si>
+  <si>
+    <t>122209-Buyers List-Tuck</t>
+  </si>
+  <si>
+    <t>Bayswater Dividend Recap</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>Add Counterparty</t>
+  </si>
+  <si>
+    <t>CounterpartiesButton</t>
+  </si>
+  <si>
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Accountant</t>
-  </si>
-  <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>HL Capital, Inc.</t>
-  </si>
-  <si>
-    <t>Do Not Disclose</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Public Equity</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Chris Lord</t>
-  </si>
-  <si>
-    <t>Yes, separate signed agreement</t>
-  </si>
-  <si>
-    <t>Cleared</t>
-  </si>
-  <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>Consulting</t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>Abrasive Form</t>
+  </si>
+  <si>
+    <t>Brian Miller</t>
   </si>
 </sst>
 </file>
@@ -723,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -737,7 +747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -745,12 +755,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -759,68 +769,116 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>43</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -832,17 +890,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -855,17 +913,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -879,13 +937,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -893,7 +951,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -901,10 +959,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -916,190 +974,193 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="T1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="U1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="V1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="Y1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="Z1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>74</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
         <v>75</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="F2" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
         <v>77</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="L2" t="s">
         <v>79</v>
       </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="M2" t="s">
         <v>80</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M2" t="s">
-        <v>86</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="R2" t="s">
+        <v>82</v>
+      </c>
+      <c r="S2" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="U2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" t="s">
+        <v>85</v>
+      </c>
+      <c r="W2" t="s">
+        <v>86</v>
+      </c>
+      <c r="X2" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="Y2" t="s">
         <v>88</v>
       </c>
-      <c r="S2" t="s">
-        <v>88</v>
-      </c>
-      <c r="T2" s="8" t="s">
+      <c r="Z2" t="s">
         <v>89</v>
       </c>
-      <c r="U2" t="s">
-        <v>90</v>
-      </c>
-      <c r="V2" t="s">
-        <v>91</v>
-      </c>
-      <c r="W2" t="s">
-        <v>92</v>
-      </c>
-      <c r="X2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>95</v>
-      </c>
       <c r="AA2" s="8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1109,16 +1170,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1129,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1140,7 +1202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1149,6 +1211,9 @@
       </c>
       <c r="C3" t="s">
         <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1158,29 +1223,26 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4780488B-FFD3-40DA-A9C2-BC61B540B5CE}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1189,19 +1251,50 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1210,57 +1303,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0D52D8-DF14-4592-92B1-516B2ED7A05F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB776725-1419-4317-8BFE-4876EE66E39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -345,7 +345,7 @@
     <t>Abrasive Form</t>
   </si>
   <si>
-    <t>Brian Miller</t>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -733,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -747,7 +747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>99</v>
       </c>
@@ -771,42 +771,42 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
@@ -819,14 +819,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -837,7 +837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -848,7 +848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -859,7 +859,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -870,7 +870,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -890,17 +890,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -913,17 +913,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -937,13 +937,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -951,7 +951,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -959,10 +959,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -974,12 +974,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1171,16 +1171,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1225,22 +1225,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4780488B-FFD3-40DA-A9C2-BC61B540B5CE}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1253,14 +1253,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1284,17 +1284,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB776725-1419-4317-8BFE-4876EE66E39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1750968B-6108-4F31-9E1F-87BFE34BAFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -156,12 +156,6 @@
     <t>Sellside</t>
   </si>
   <si>
-    <t>Debt Capital Markets</t>
-  </si>
-  <si>
-    <t>Equity Capital Markets</t>
-  </si>
-  <si>
     <t>Job Types</t>
   </si>
   <si>
@@ -346,6 +340,12 @@
   </si>
   <si>
     <t>Jennie Stewart</t>
+  </si>
+  <si>
+    <t>Debt Financing</t>
+  </si>
+  <si>
+    <t>Equity Placements</t>
   </si>
 </sst>
 </file>
@@ -757,10 +757,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -808,7 +808,7 @@
     </row>
     <row r="7" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -831,54 +831,54 @@
         <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -981,186 +981,186 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="R1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="S1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="V1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
         <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" t="s">
         <v>75</v>
       </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" t="s">
         <v>76</v>
       </c>
-      <c r="G2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="L2" t="s">
         <v>77</v>
       </c>
-      <c r="I2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>78</v>
-      </c>
-      <c r="L2" t="s">
-        <v>79</v>
-      </c>
-      <c r="M2" t="s">
-        <v>80</v>
       </c>
       <c r="N2" t="s">
         <v>0</v>
       </c>
       <c r="O2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="R2" t="s">
+        <v>80</v>
+      </c>
+      <c r="S2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T2" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>82</v>
       </c>
-      <c r="S2" t="s">
-        <v>82</v>
-      </c>
-      <c r="T2" s="8" t="s">
+      <c r="V2" t="s">
         <v>83</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>84</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>85</v>
       </c>
-      <c r="W2" t="s">
+      <c r="Y2" t="s">
         <v>86</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>87</v>
       </c>
-      <c r="Y2" t="s">
-        <v>88</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>89</v>
-      </c>
       <c r="AA2" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AB2" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AC2" t="s">
         <v>0</v>
       </c>
       <c r="AD2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1213,7 +1213,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1232,17 +1232,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
+++ b/TestData/TMTI0063927_VerifyViewCounterpartiesButtonAndViewsOnSalesforceLightningVersion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1750968B-6108-4F31-9E1F-87BFE34BAFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADEC8EE-9EB2-4135-916B-114EE72F4F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -733,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -747,7 +747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -771,42 +771,42 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3FF30-5810-42A4-B6D3-B7BD65EBF170}">
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>39</v>
       </c>
@@ -819,14 +819,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30953EE-CA2E-4F7C-B9BA-21629FCB862C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -837,7 +837,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -848,7 +848,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -859,7 +859,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -870,7 +870,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -890,17 +890,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -913,17 +913,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -937,13 +937,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398F625-8674-4D63-93D8-B47E3A580505}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -951,7 +951,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -959,10 +959,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J11" s="2"/>
     </row>
   </sheetData>
@@ -974,12 +974,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -1171,16 +1171,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F94DFB-4724-4A5C-994B-DCCD1086734F}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1225,22 +1225,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4780488B-FFD3-40DA-A9C2-BC61B540B5CE}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1253,14 +1253,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{751812A8-ABA8-4232-9D81-14F299F55479}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1284,17 +1284,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7552AB4B-37A5-4D47-8C03-7FFC70E2819F}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
